--- a/output/pdf_financials_xlsx/TIGR.xlsx
+++ b/output/pdf_financials_xlsx/TIGR.xlsx
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.067828</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.067828</v>
       </c>
     </row>
     <row r="93">
@@ -2452,7 +2452,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.067828</v>
       </c>

--- a/output/pdf_financials_xlsx/TIGR.xlsx
+++ b/output/pdf_financials_xlsx/TIGR.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.425992</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.343221</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.425992</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.343221</v>
       </c>
     </row>
     <row r="37">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
